--- a/output/yearly_benthic_cover_iteration_47_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_47_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.15981202436959</v>
+        <v>45.39359396659666</v>
       </c>
       <c r="M2" t="n">
-        <v>100.2521115172704</v>
+        <v>99.90155979197704</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.08493218134392</v>
+        <v>87.9833703813396</v>
       </c>
       <c r="C3" t="n">
-        <v>45.96179040123673</v>
+        <v>45.93696922855027</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228853249652361</v>
+        <v>2.22861156521616</v>
       </c>
       <c r="E3" t="n">
-        <v>5.72837966915206</v>
+        <v>5.708561544662318</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429510832174537</v>
+        <v>0.7428705217387201</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98401845449362</v>
+        <v>33.97648174076863</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17574982800286</v>
+        <v>34.17204399998112</v>
       </c>
       <c r="I3" t="n">
-        <v>6.581535626716475</v>
+        <v>6.511860248105637</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643444270109086</v>
+        <v>4.642940760867001</v>
       </c>
       <c r="K3" t="n">
-        <v>11.91506781865609</v>
+        <v>12.01662961866042</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88691140010371</v>
+        <v>48.81264627689288</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7637696199965</v>
+        <v>106.7662451241036</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.20334543747478</v>
+        <v>87.01887788146205</v>
       </c>
       <c r="C4" t="n">
-        <v>42.71671788302365</v>
+        <v>42.59645790696739</v>
       </c>
       <c r="D4" t="n">
-        <v>2.186587876926812</v>
+        <v>2.181863471087262</v>
       </c>
       <c r="E4" t="n">
-        <v>6.53577595740424</v>
+        <v>6.495125834577454</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445119407223394</v>
+        <v>0.7444179335914853</v>
       </c>
       <c r="G4" t="n">
-        <v>33.33958517611824</v>
+        <v>33.26377980949593</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24754927322761</v>
+        <v>34.24322494520832</v>
       </c>
       <c r="I4" t="n">
-        <v>5.496135583560928</v>
+        <v>5.437853802554816</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653199629514622</v>
+        <v>4.652612084946783</v>
       </c>
       <c r="K4" t="n">
-        <v>12.79665456252522</v>
+        <v>12.98112211853797</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30380712037568</v>
+        <v>44.24153496760282</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81717956592455</v>
+        <v>99.81911499310817</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.17338970235642</v>
+        <v>85.68126002140423</v>
       </c>
       <c r="C5" t="n">
-        <v>42.53985738043675</v>
+        <v>42.10282666127139</v>
       </c>
       <c r="D5" t="n">
-        <v>2.136831441115373</v>
+        <v>2.116007660749096</v>
       </c>
       <c r="E5" t="n">
-        <v>7.151759465813666</v>
+        <v>7.05567289311811</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458333079608049</v>
+        <v>0.7457326204530016</v>
       </c>
       <c r="G5" t="n">
-        <v>32.58093332987868</v>
+        <v>32.25976961211494</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30833216619702</v>
+        <v>34.30370054083807</v>
       </c>
       <c r="I5" t="n">
-        <v>4.588241816635847</v>
+        <v>4.539547816299753</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661458174755031</v>
+        <v>4.66082887783126</v>
       </c>
       <c r="K5" t="n">
-        <v>13.82661029764357</v>
+        <v>14.31873997859577</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48086188904301</v>
+        <v>43.42738186561745</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84732956712332</v>
+        <v>99.8489485054846</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.90895638900942</v>
+        <v>84.0903495307969</v>
       </c>
       <c r="C6" t="n">
-        <v>41.98818003928761</v>
+        <v>41.21676504809164</v>
       </c>
       <c r="D6" t="n">
-        <v>2.075415742686917</v>
+        <v>2.037811709261643</v>
       </c>
       <c r="E6" t="n">
-        <v>7.584421101100603</v>
+        <v>7.426373842029762</v>
       </c>
       <c r="F6" t="n">
-        <v>0.746954511473111</v>
+        <v>0.7468525709243813</v>
       </c>
       <c r="G6" t="n">
-        <v>31.64450908161837</v>
+        <v>31.06762677332563</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3599075277631</v>
+        <v>34.35521826252153</v>
       </c>
       <c r="I6" t="n">
-        <v>3.829282727660369</v>
+        <v>3.788637804456555</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668465696706944</v>
+        <v>4.667828568277383</v>
       </c>
       <c r="K6" t="n">
-        <v>15.09104361099057</v>
+        <v>15.90965046920312</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79332518814859</v>
+        <v>42.74748593225245</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87254883842678</v>
+        <v>99.87390144954722</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.48527370421773</v>
+        <v>82.38050577337123</v>
       </c>
       <c r="C7" t="n">
-        <v>41.15946257537348</v>
+        <v>40.09502083317917</v>
       </c>
       <c r="D7" t="n">
-        <v>2.006436497099664</v>
+        <v>1.954342802498359</v>
       </c>
       <c r="E7" t="n">
-        <v>7.864865934755229</v>
+        <v>7.64906182997407</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479074237028845</v>
+        <v>0.7478078849937857</v>
       </c>
       <c r="G7" t="n">
-        <v>30.59276107829878</v>
+        <v>29.79509465923801</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40374149033268</v>
+        <v>34.39916270971413</v>
       </c>
       <c r="I7" t="n">
-        <v>3.195139881885474</v>
+        <v>3.161236605741713</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674421398143028</v>
+        <v>4.673799281211161</v>
       </c>
       <c r="K7" t="n">
-        <v>16.51472629578225</v>
+        <v>17.61949422662877</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21944216418702</v>
+        <v>42.18024500117938</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89363103534275</v>
+        <v>99.89476006098732</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.44566336658599</v>
+        <v>87.46603045505971</v>
       </c>
       <c r="C8" t="n">
-        <v>43.48635050742669</v>
+        <v>42.46526445096152</v>
       </c>
       <c r="D8" t="n">
-        <v>2.010749522252612</v>
+        <v>1.95862477594149</v>
       </c>
       <c r="E8" t="n">
-        <v>9.718155127764813</v>
+        <v>9.534577115227346</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495151214970436</v>
+        <v>0.7494463352697629</v>
       </c>
       <c r="G8" t="n">
-        <v>31.10140876216402</v>
+        <v>30.31565780064872</v>
       </c>
       <c r="H8" t="n">
-        <v>34.477695588864</v>
+        <v>34.47453142240909</v>
       </c>
       <c r="I8" t="n">
-        <v>5.70366973468697</v>
+        <v>5.749153410127283</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684469509356522</v>
+        <v>4.684039595436019</v>
       </c>
       <c r="K8" t="n">
-        <v>11.55433663341401</v>
+        <v>12.53396954494029</v>
       </c>
       <c r="L8" t="n">
-        <v>44.76959834397596</v>
+        <v>44.8095465198023</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81028548481666</v>
+        <v>99.80878051570411</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.6109505240685</v>
+        <v>85.27068149506819</v>
       </c>
       <c r="C9" t="n">
-        <v>42.53729204320085</v>
+        <v>41.16145059628013</v>
       </c>
       <c r="D9" t="n">
-        <v>1.928142584809485</v>
+        <v>1.85926110052088</v>
       </c>
       <c r="E9" t="n">
-        <v>10.11253558852406</v>
+        <v>9.850866953258128</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508887036374917</v>
+        <v>0.7508525651817491</v>
       </c>
       <c r="G9" t="n">
-        <v>29.82368018405102</v>
+        <v>28.77770361010297</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54088036732462</v>
+        <v>34.53921799836046</v>
       </c>
       <c r="I9" t="n">
-        <v>4.76176869798749</v>
+        <v>4.799950735258063</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693054397734323</v>
+        <v>4.692828532385933</v>
       </c>
       <c r="K9" t="n">
-        <v>13.38904947593151</v>
+        <v>14.72931850493181</v>
       </c>
       <c r="L9" t="n">
-        <v>43.91522321045966</v>
+        <v>43.94953219295117</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84156472959202</v>
+        <v>99.84030129416313</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.59443164489831</v>
+        <v>82.87718973208383</v>
       </c>
       <c r="C10" t="n">
-        <v>41.26008494546125</v>
+        <v>39.5118522904208</v>
       </c>
       <c r="D10" t="n">
-        <v>1.83814208364269</v>
+        <v>1.75216728803383</v>
       </c>
       <c r="E10" t="n">
-        <v>10.30290214843605</v>
+        <v>9.951189107979024</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520646274385184</v>
+        <v>0.7520624755067392</v>
       </c>
       <c r="G10" t="n">
-        <v>28.43159114232281</v>
+        <v>27.12010210735284</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59497286217185</v>
+        <v>34.59487387331</v>
       </c>
       <c r="I10" t="n">
-        <v>3.974354859395653</v>
+        <v>4.006404407984298</v>
       </c>
       <c r="J10" t="n">
-        <v>4.70040392149074</v>
+        <v>4.700390471917121</v>
       </c>
       <c r="K10" t="n">
-        <v>15.40556835510169</v>
+        <v>17.12281026791613</v>
       </c>
       <c r="L10" t="n">
-        <v>43.20207534671518</v>
+        <v>43.23200547679478</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86772864727813</v>
+        <v>99.86666803513172</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.31296279435107</v>
+        <v>80.44568342271135</v>
       </c>
       <c r="C11" t="n">
-        <v>39.59522488176446</v>
+        <v>37.7004597261644</v>
       </c>
       <c r="D11" t="n">
-        <v>1.737110027348836</v>
+        <v>1.644704655723455</v>
       </c>
       <c r="E11" t="n">
-        <v>10.28934617249102</v>
+        <v>9.898086026496554</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530746566609934</v>
+        <v>0.753104324268692</v>
       </c>
       <c r="G11" t="n">
-        <v>26.86887075069644</v>
+        <v>25.45679199941638</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6414342064057</v>
+        <v>34.64279891635983</v>
       </c>
       <c r="I11" t="n">
-        <v>3.316410376616879</v>
+        <v>3.34329547376711</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706716604131208</v>
+        <v>4.706902026679326</v>
       </c>
       <c r="K11" t="n">
-        <v>17.68703720564892</v>
+        <v>19.55431657728866</v>
       </c>
       <c r="L11" t="n">
-        <v>42.6073391664923</v>
+        <v>42.63393468521403</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88960125390568</v>
+        <v>99.8887109886671</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.97900077637907</v>
+        <v>77.9060872308812</v>
       </c>
       <c r="C12" t="n">
-        <v>37.77505214153318</v>
+        <v>35.67743740765368</v>
       </c>
       <c r="D12" t="n">
-        <v>1.634755566398248</v>
+        <v>1.53364278608066</v>
       </c>
       <c r="E12" t="n">
-        <v>10.14421828259327</v>
+        <v>9.694599369817698</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539430737207472</v>
+        <v>0.7540031469545201</v>
       </c>
       <c r="G12" t="n">
-        <v>25.2856959726222</v>
+        <v>23.73777277932468</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68138139115437</v>
+        <v>34.68414475990792</v>
       </c>
       <c r="I12" t="n">
-        <v>2.766862279135551</v>
+        <v>2.789404720329972</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712144210754669</v>
+        <v>4.712519668465752</v>
       </c>
       <c r="K12" t="n">
-        <v>20.02099922362093</v>
+        <v>22.09391276911882</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11182612438431</v>
+        <v>42.13578050451174</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90787748953842</v>
+        <v>99.90713068128423</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.56083986217587</v>
+        <v>75.32825264325257</v>
       </c>
       <c r="C13" t="n">
-        <v>35.784738408789</v>
+        <v>33.52960081681701</v>
       </c>
       <c r="D13" t="n">
-        <v>1.529617127070345</v>
+        <v>1.422039225921071</v>
       </c>
       <c r="E13" t="n">
-        <v>9.876465856848233</v>
+        <v>9.376937239904654</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546909188387259</v>
+        <v>0.7547795214244757</v>
       </c>
       <c r="G13" t="n">
-        <v>23.65945981443089</v>
+        <v>22.01036925584689</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71578226658139</v>
+        <v>34.71985798552588</v>
       </c>
       <c r="I13" t="n">
-        <v>2.308005635664256</v>
+        <v>2.326897405726635</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716818242742035</v>
+        <v>4.717372008902974</v>
       </c>
       <c r="K13" t="n">
-        <v>22.43916013782412</v>
+        <v>24.67174735674742</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69924416785534</v>
+        <v>41.72116836198199</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92314271446845</v>
+        <v>99.92251653554642</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.06804117585008</v>
+        <v>82.60113339111859</v>
       </c>
       <c r="C14" t="n">
-        <v>39.8158368066327</v>
+        <v>38.03263438429528</v>
       </c>
       <c r="D14" t="n">
-        <v>1.531420748239304</v>
+        <v>1.423791355194016</v>
       </c>
       <c r="E14" t="n">
-        <v>12.13608712083747</v>
+        <v>11.87993542993515</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555807993801694</v>
+        <v>0.7557095037132909</v>
       </c>
       <c r="G14" t="n">
-        <v>25.43969628281493</v>
+        <v>24.02005903347566</v>
       </c>
       <c r="H14" t="n">
-        <v>36.50905560338997</v>
+        <v>36.74520743473158</v>
       </c>
       <c r="I14" t="n">
-        <v>2.973820625062186</v>
+        <v>3.053246235860818</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722379996126058</v>
+        <v>4.723184398208069</v>
       </c>
       <c r="K14" t="n">
-        <v>15.93195882414992</v>
+        <v>17.39886660888142</v>
       </c>
       <c r="L14" t="n">
-        <v>44.1531937616675</v>
+        <v>44.46684937728662</v>
       </c>
       <c r="M14" t="n">
-        <v>99.9009893924501</v>
+        <v>99.89835037046332</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.28971159592321</v>
+        <v>81.73926689903736</v>
       </c>
       <c r="C15" t="n">
-        <v>39.49622283166862</v>
+        <v>37.62933060384331</v>
       </c>
       <c r="D15" t="n">
-        <v>1.502283264162734</v>
+        <v>1.390942435755344</v>
       </c>
       <c r="E15" t="n">
-        <v>12.31988572050154</v>
+        <v>12.04272367200901</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563309228730539</v>
+        <v>0.7564944398647448</v>
       </c>
       <c r="G15" t="n">
-        <v>24.95693387900275</v>
+        <v>23.47825468039962</v>
       </c>
       <c r="H15" t="n">
-        <v>36.546565402444</v>
+        <v>36.79574678459664</v>
       </c>
       <c r="I15" t="n">
-        <v>2.480644138982555</v>
+        <v>2.547014637257331</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727068267956586</v>
+        <v>4.728090249154656</v>
       </c>
       <c r="K15" t="n">
-        <v>16.71028840407679</v>
+        <v>18.26073310096265</v>
       </c>
       <c r="L15" t="n">
-        <v>43.71088263578064</v>
+        <v>44.02512389975347</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91739387152604</v>
+        <v>99.91518760455943</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.73226864383732</v>
+        <v>78.97392905310016</v>
       </c>
       <c r="C16" t="n">
-        <v>37.32252474264619</v>
+        <v>35.25682941504392</v>
       </c>
       <c r="D16" t="n">
-        <v>1.40440788242421</v>
+        <v>1.287890702748512</v>
       </c>
       <c r="E16" t="n">
-        <v>11.86206004923965</v>
+        <v>11.50457514496528</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569770195462601</v>
+        <v>0.7571727685470868</v>
       </c>
       <c r="G16" t="n">
-        <v>23.33096260667293</v>
+        <v>21.73880467111359</v>
       </c>
       <c r="H16" t="n">
-        <v>36.57778535340664</v>
+        <v>36.82874056368727</v>
       </c>
       <c r="I16" t="n">
-        <v>2.068969360383504</v>
+        <v>2.124415398619115</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731106372164124</v>
+        <v>4.732329803419293</v>
       </c>
       <c r="K16" t="n">
-        <v>19.26773135616269</v>
+        <v>21.02607094689985</v>
       </c>
       <c r="L16" t="n">
-        <v>43.34083711955272</v>
+        <v>43.64634923146574</v>
       </c>
       <c r="M16" t="n">
-        <v>99.9310932183616</v>
+        <v>99.92924959340951</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.25459608647354</v>
+        <v>80.83737455305398</v>
       </c>
       <c r="C17" t="n">
-        <v>38.44694070251445</v>
+        <v>36.59737392512615</v>
       </c>
       <c r="D17" t="n">
-        <v>1.405578568591986</v>
+        <v>1.28902340040463</v>
       </c>
       <c r="E17" t="n">
-        <v>12.59008439593257</v>
+        <v>12.34747514841778</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576080203667463</v>
+        <v>0.7578387006936422</v>
       </c>
       <c r="G17" t="n">
-        <v>23.72571831421466</v>
+        <v>22.23522400297928</v>
       </c>
       <c r="H17" t="n">
-        <v>36.98358334599295</v>
+        <v>37.33843146819497</v>
       </c>
       <c r="I17" t="n">
-        <v>2.056973314082467</v>
+        <v>2.13288995302841</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735050127292164</v>
+        <v>4.736491879335264</v>
       </c>
       <c r="K17" t="n">
-        <v>17.74540391352646</v>
+        <v>19.16262544694602</v>
       </c>
       <c r="L17" t="n">
-        <v>43.73914671427234</v>
+        <v>44.16896677031571</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93149133031325</v>
+        <v>99.92896614238788</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.76728919037903</v>
+        <v>78.19568783046665</v>
       </c>
       <c r="C18" t="n">
-        <v>36.27737314107846</v>
+        <v>34.2841092456064</v>
       </c>
       <c r="D18" t="n">
-        <v>1.313837360492754</v>
+        <v>1.195001796032551</v>
       </c>
       <c r="E18" t="n">
-        <v>12.05423322238959</v>
+        <v>11.74330737127004</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581510919622021</v>
+        <v>0.758413331760775</v>
       </c>
       <c r="G18" t="n">
-        <v>22.17715595718575</v>
+        <v>20.6133826666029</v>
       </c>
       <c r="H18" t="n">
-        <v>37.01009406535368</v>
+        <v>37.36674332756556</v>
       </c>
       <c r="I18" t="n">
-        <v>1.715373168231293</v>
+        <v>1.778756013729983</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738444324763762</v>
+        <v>4.740083323504844</v>
       </c>
       <c r="K18" t="n">
-        <v>20.23271080962096</v>
+        <v>21.80431216953334</v>
       </c>
       <c r="L18" t="n">
-        <v>43.43277790168717</v>
+        <v>43.85233164172057</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9428618523866</v>
+        <v>99.94075305686033</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.68665003988343</v>
+        <v>77.16490182839273</v>
       </c>
       <c r="C19" t="n">
-        <v>35.46098475490017</v>
+        <v>33.51995207057337</v>
       </c>
       <c r="D19" t="n">
-        <v>1.274666212488333</v>
+        <v>1.15876825046821</v>
       </c>
       <c r="E19" t="n">
-        <v>11.9332352670439</v>
+        <v>11.63548356186285</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586104738732242</v>
+        <v>0.7589013037504559</v>
       </c>
       <c r="G19" t="n">
-        <v>21.51595946176089</v>
+        <v>19.98836608289123</v>
       </c>
       <c r="H19" t="n">
-        <v>37.0325193680659</v>
+        <v>37.39078552635856</v>
       </c>
       <c r="I19" t="n">
-        <v>1.430343794943528</v>
+        <v>1.489463954621069</v>
       </c>
       <c r="J19" t="n">
-        <v>4.74131546170765</v>
+        <v>4.74313314844035</v>
       </c>
       <c r="K19" t="n">
-        <v>21.31334996011655</v>
+        <v>22.83509817160728</v>
       </c>
       <c r="L19" t="n">
-        <v>43.17801603031018</v>
+        <v>43.59533288340808</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95235074532691</v>
+        <v>99.95038312558873</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.0424402256962</v>
+        <v>74.51207226936219</v>
       </c>
       <c r="C20" t="n">
-        <v>33.03692046138794</v>
+        <v>31.0955596336396</v>
       </c>
       <c r="D20" t="n">
-        <v>1.178216439970879</v>
+        <v>1.065590284360095</v>
       </c>
       <c r="E20" t="n">
-        <v>11.22904957222616</v>
+        <v>10.90684508489312</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590070510355391</v>
+        <v>0.759322929736433</v>
       </c>
       <c r="G20" t="n">
-        <v>19.88791803785707</v>
+        <v>18.38107722536888</v>
       </c>
       <c r="H20" t="n">
-        <v>37.05187877839591</v>
+        <v>37.41155888217715</v>
       </c>
       <c r="I20" t="n">
-        <v>1.192576277238535</v>
+        <v>1.241909551973811</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743794068972118</v>
+        <v>4.745768310852706</v>
       </c>
       <c r="K20" t="n">
-        <v>23.95755977430379</v>
+        <v>25.4879277306378</v>
       </c>
       <c r="L20" t="n">
-        <v>42.96578799222649</v>
+        <v>43.37513863698313</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96026822791822</v>
+        <v>99.95862600126054</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.94542409945214</v>
+        <v>80.99631950637153</v>
       </c>
       <c r="C21" t="n">
-        <v>36.69716124654641</v>
+        <v>35.15466391768036</v>
       </c>
       <c r="D21" t="n">
-        <v>1.179039896798966</v>
+        <v>1.066358695361545</v>
       </c>
       <c r="E21" t="n">
-        <v>13.20283505707659</v>
+        <v>13.08310040313685</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595375219384548</v>
+        <v>0.7598704873685048</v>
       </c>
       <c r="G21" t="n">
-        <v>21.58139645903034</v>
+        <v>20.27068481680109</v>
       </c>
       <c r="H21" t="n">
-        <v>38.75735311151654</v>
+        <v>39.31488960123414</v>
       </c>
       <c r="I21" t="n">
-        <v>1.718152540975909</v>
+        <v>1.752224956416252</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747109512115341</v>
+        <v>4.749190546053155</v>
       </c>
       <c r="K21" t="n">
-        <v>18.05457590054786</v>
+        <v>19.00368049362847</v>
       </c>
       <c r="L21" t="n">
-        <v>45.19103110087732</v>
+        <v>45.78329017819993</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9427682479716</v>
+        <v>99.94163458950875</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_47_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_47_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.39359396659666</v>
+        <v>45.64298737301479</v>
       </c>
       <c r="M2" t="n">
-        <v>99.90155979197704</v>
+        <v>98.97061130474532</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.9833703813396</v>
+        <v>87.92962951200913</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93696922855027</v>
+        <v>45.88087393732962</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22861156521616</v>
+        <v>2.228516087881618</v>
       </c>
       <c r="E3" t="n">
-        <v>5.708561544662318</v>
+        <v>5.673709723820384</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428705217387201</v>
+        <v>0.7428386959605395</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97648174076863</v>
+        <v>33.95754619875726</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17204399998112</v>
+        <v>34.17058001418481</v>
       </c>
       <c r="I3" t="n">
-        <v>6.511860248105637</v>
+        <v>6.513696941651128</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642940760867001</v>
+        <v>4.642741849753372</v>
       </c>
       <c r="K3" t="n">
-        <v>12.01662961866042</v>
+        <v>12.07037048799089</v>
       </c>
       <c r="L3" t="n">
-        <v>48.81264627689288</v>
+        <v>48.81492474968982</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7662451241036</v>
+        <v>106.7661691750103</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.01887788146205</v>
+        <v>86.96605940038383</v>
       </c>
       <c r="C4" t="n">
-        <v>42.59645790696739</v>
+        <v>42.54372072557938</v>
       </c>
       <c r="D4" t="n">
-        <v>2.181863471087262</v>
+        <v>2.181757099414274</v>
       </c>
       <c r="E4" t="n">
-        <v>6.495125834577454</v>
+        <v>6.461229549135017</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444179335914853</v>
+        <v>0.7443874208628843</v>
       </c>
       <c r="G4" t="n">
-        <v>33.26377980949593</v>
+        <v>33.24504494300175</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24322494520832</v>
+        <v>34.24182135969268</v>
       </c>
       <c r="I4" t="n">
-        <v>5.437853802554816</v>
+        <v>5.439397647884189</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652612084946783</v>
+        <v>4.652421380393027</v>
       </c>
       <c r="K4" t="n">
-        <v>12.98112211853797</v>
+        <v>13.03394059961619</v>
       </c>
       <c r="L4" t="n">
-        <v>44.24153496760282</v>
+        <v>44.24140264864746</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81911499310817</v>
+        <v>99.81906397384301</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.68126002140423</v>
+        <v>85.66041950748195</v>
       </c>
       <c r="C5" t="n">
-        <v>42.10282666127139</v>
+        <v>42.08225101505153</v>
       </c>
       <c r="D5" t="n">
-        <v>2.116007660749096</v>
+        <v>2.117487239619543</v>
       </c>
       <c r="E5" t="n">
-        <v>7.05567289311811</v>
+        <v>7.027702467558918</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457326204530016</v>
+        <v>0.7457027482263286</v>
       </c>
       <c r="G5" t="n">
-        <v>32.25976961211494</v>
+        <v>32.2657176026989</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30370054083807</v>
+        <v>34.30232641841111</v>
       </c>
       <c r="I5" t="n">
-        <v>4.539547816299753</v>
+        <v>4.540840854552597</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66082887783126</v>
+        <v>4.660642176414553</v>
       </c>
       <c r="K5" t="n">
-        <v>14.31873997859577</v>
+        <v>14.33958049251806</v>
       </c>
       <c r="L5" t="n">
-        <v>43.42738186561745</v>
+        <v>43.42707411332253</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8489485054846</v>
+        <v>99.84890562089211</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.0903495307969</v>
+        <v>84.05584692325668</v>
       </c>
       <c r="C6" t="n">
-        <v>41.21676504809164</v>
+        <v>41.1827098147885</v>
       </c>
       <c r="D6" t="n">
-        <v>2.037811709261643</v>
+        <v>2.038498703790503</v>
       </c>
       <c r="E6" t="n">
-        <v>7.426373842029762</v>
+        <v>7.397168535433005</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468525709243813</v>
+        <v>0.7468234338192851</v>
       </c>
       <c r="G6" t="n">
-        <v>31.06762677332563</v>
+        <v>31.06211092057865</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35521826252153</v>
+        <v>34.35387795568711</v>
       </c>
       <c r="I6" t="n">
-        <v>3.788637804456555</v>
+        <v>3.789720912577577</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667828568277383</v>
+        <v>4.667646461370532</v>
       </c>
       <c r="K6" t="n">
-        <v>15.90965046920312</v>
+        <v>15.94415307674333</v>
       </c>
       <c r="L6" t="n">
-        <v>42.74748593225245</v>
+        <v>42.74700264028616</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87390144954722</v>
+        <v>99.87386553181798</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.38050577337123</v>
+        <v>82.28158414216244</v>
       </c>
       <c r="C7" t="n">
-        <v>40.09502083317917</v>
+        <v>39.99668893927412</v>
       </c>
       <c r="D7" t="n">
-        <v>1.954342802498359</v>
+        <v>1.951686263952242</v>
       </c>
       <c r="E7" t="n">
-        <v>7.64906182997407</v>
+        <v>7.609173721944708</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478078849937857</v>
+        <v>0.7477801343315265</v>
       </c>
       <c r="G7" t="n">
-        <v>29.79509465923801</v>
+        <v>29.73928563227802</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39916270971413</v>
+        <v>34.39788617925021</v>
       </c>
       <c r="I7" t="n">
-        <v>3.161236605741713</v>
+        <v>3.162146370833698</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673799281211161</v>
+        <v>4.673625839572041</v>
       </c>
       <c r="K7" t="n">
-        <v>17.61949422662877</v>
+        <v>17.71841585783754</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18024500117938</v>
+        <v>42.17962517753895</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89476006098732</v>
+        <v>99.89472997465062</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.46603045505971</v>
+        <v>87.16139698251179</v>
       </c>
       <c r="C8" t="n">
-        <v>42.46526445096152</v>
+        <v>42.21739990697387</v>
       </c>
       <c r="D8" t="n">
-        <v>1.95862477594149</v>
+        <v>1.955937262579417</v>
       </c>
       <c r="E8" t="n">
-        <v>9.534577115227346</v>
+        <v>9.391626418761371</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494463352697629</v>
+        <v>0.7494088860336747</v>
       </c>
       <c r="G8" t="n">
-        <v>30.31565780064872</v>
+        <v>30.21238172405257</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47453142240909</v>
+        <v>34.47280875754903</v>
       </c>
       <c r="I8" t="n">
-        <v>5.749153410127283</v>
+        <v>5.695428395825255</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684039595436019</v>
+        <v>4.683805537710468</v>
       </c>
       <c r="K8" t="n">
-        <v>12.53396954494029</v>
+        <v>12.83860301748823</v>
       </c>
       <c r="L8" t="n">
-        <v>44.8095465198023</v>
+        <v>44.75456207370834</v>
       </c>
       <c r="M8" t="n">
-        <v>99.80878051570411</v>
+        <v>99.81056499817043</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.27068149506819</v>
+        <v>84.93822839817666</v>
       </c>
       <c r="C9" t="n">
-        <v>41.16145059628013</v>
+        <v>40.87721742873434</v>
       </c>
       <c r="D9" t="n">
-        <v>1.85926110052088</v>
+        <v>1.854762886565128</v>
       </c>
       <c r="E9" t="n">
-        <v>9.850866953258128</v>
+        <v>9.698335485803254</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508525651817491</v>
+        <v>0.750807343328146</v>
       </c>
       <c r="G9" t="n">
-        <v>28.77770361010297</v>
+        <v>28.64959189059676</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53921799836046</v>
+        <v>34.53713779309471</v>
       </c>
       <c r="I9" t="n">
-        <v>4.799950735258063</v>
+        <v>4.755047102987752</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692828532385933</v>
+        <v>4.692545895800913</v>
       </c>
       <c r="K9" t="n">
-        <v>14.72931850493181</v>
+        <v>15.06177160182332</v>
       </c>
       <c r="L9" t="n">
-        <v>43.94953219295117</v>
+        <v>43.90280462511388</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84030129416313</v>
+        <v>99.84179365567155</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.87718973208383</v>
+        <v>82.50332043066362</v>
       </c>
       <c r="C10" t="n">
-        <v>39.5118522904208</v>
+        <v>39.17901284752852</v>
       </c>
       <c r="D10" t="n">
-        <v>1.75216728803383</v>
+        <v>1.745221727386077</v>
       </c>
       <c r="E10" t="n">
-        <v>9.951189107979024</v>
+        <v>9.787039953061496</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520624755067392</v>
+        <v>0.7520112844614399</v>
       </c>
       <c r="G10" t="n">
-        <v>27.12010210735284</v>
+        <v>26.95756455468505</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59487387331</v>
+        <v>34.59251908522624</v>
       </c>
       <c r="I10" t="n">
-        <v>4.006404407984298</v>
+        <v>3.968893297959323</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700390471917121</v>
+        <v>4.700070527884001</v>
       </c>
       <c r="K10" t="n">
-        <v>17.12281026791613</v>
+        <v>17.49667956933639</v>
       </c>
       <c r="L10" t="n">
-        <v>43.23200547679478</v>
+        <v>43.19222294138542</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86666803513172</v>
+        <v>99.86791535825033</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.44568342271135</v>
+        <v>79.89652632177739</v>
       </c>
       <c r="C11" t="n">
-        <v>37.7004597261644</v>
+        <v>37.18627859097997</v>
       </c>
       <c r="D11" t="n">
-        <v>1.644704655723455</v>
+        <v>1.62927157086785</v>
       </c>
       <c r="E11" t="n">
-        <v>9.898086026496554</v>
+        <v>9.688799203315517</v>
       </c>
       <c r="F11" t="n">
-        <v>0.753104324268692</v>
+        <v>0.7530503981528359</v>
       </c>
       <c r="G11" t="n">
-        <v>25.45679199941638</v>
+        <v>25.16654065186696</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64279891635983</v>
+        <v>34.64031831503045</v>
       </c>
       <c r="I11" t="n">
-        <v>3.34329547376711</v>
+        <v>3.311981194088543</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706902026679326</v>
+        <v>4.706564988455225</v>
       </c>
       <c r="K11" t="n">
-        <v>19.55431657728866</v>
+        <v>20.10347367822261</v>
       </c>
       <c r="L11" t="n">
-        <v>42.63393468521403</v>
+        <v>42.60000069474301</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8887109886671</v>
+        <v>99.8897529639456</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.9060872308812</v>
+        <v>77.2615552284622</v>
       </c>
       <c r="C12" t="n">
-        <v>35.67743740765368</v>
+        <v>35.06268811895584</v>
       </c>
       <c r="D12" t="n">
-        <v>1.53364278608066</v>
+        <v>1.513405328411468</v>
       </c>
       <c r="E12" t="n">
-        <v>9.694599369817698</v>
+        <v>9.460322496134882</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7540031469545201</v>
+        <v>0.7539481646693419</v>
       </c>
       <c r="G12" t="n">
-        <v>23.73777277932468</v>
+        <v>23.37681292746777</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68414475990792</v>
+        <v>34.68161557478972</v>
       </c>
       <c r="I12" t="n">
-        <v>2.789404720329972</v>
+        <v>2.763274707805633</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712519668465752</v>
+        <v>4.712176029183388</v>
       </c>
       <c r="K12" t="n">
-        <v>22.09391276911882</v>
+        <v>22.73844477153779</v>
       </c>
       <c r="L12" t="n">
-        <v>42.13578050451174</v>
+        <v>42.1068676318928</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90713068128423</v>
+        <v>99.90800052238643</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.32825264325257</v>
+        <v>74.64022778070726</v>
       </c>
       <c r="C13" t="n">
-        <v>33.52960081681701</v>
+        <v>32.8669496227904</v>
       </c>
       <c r="D13" t="n">
-        <v>1.422039225921071</v>
+        <v>1.399354759400129</v>
       </c>
       <c r="E13" t="n">
-        <v>9.376937239904654</v>
+        <v>9.131573681491728</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547795214244757</v>
+        <v>0.7547242990784411</v>
       </c>
       <c r="G13" t="n">
-        <v>22.01036925584689</v>
+        <v>21.61513099996471</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71985798552588</v>
+        <v>34.71731775760828</v>
       </c>
       <c r="I13" t="n">
-        <v>2.326897405726635</v>
+        <v>2.305099413923712</v>
       </c>
       <c r="J13" t="n">
-        <v>4.717372008902974</v>
+        <v>4.717026869240257</v>
       </c>
       <c r="K13" t="n">
-        <v>24.67174735674742</v>
+        <v>25.35977221929273</v>
       </c>
       <c r="L13" t="n">
-        <v>41.72116836198199</v>
+        <v>41.69652052714447</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92251653554642</v>
+        <v>99.92324236922761</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.60113339111859</v>
+        <v>82.08924032064726</v>
       </c>
       <c r="C14" t="n">
-        <v>38.03263438429528</v>
+        <v>37.40888865473728</v>
       </c>
       <c r="D14" t="n">
-        <v>1.423791355194016</v>
+        <v>1.401146633481525</v>
       </c>
       <c r="E14" t="n">
-        <v>11.87993542993515</v>
+        <v>11.66299366203275</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7557095037132909</v>
+        <v>0.7556907237116757</v>
       </c>
       <c r="G14" t="n">
-        <v>24.02005903347566</v>
+        <v>23.63695972577397</v>
       </c>
       <c r="H14" t="n">
-        <v>36.74520743473158</v>
+        <v>36.75592383648182</v>
       </c>
       <c r="I14" t="n">
-        <v>3.053246235860818</v>
+        <v>3.153458715967542</v>
       </c>
       <c r="J14" t="n">
-        <v>4.723184398208069</v>
+        <v>4.723067023197974</v>
       </c>
       <c r="K14" t="n">
-        <v>17.39886660888142</v>
+        <v>17.91075967935275</v>
       </c>
       <c r="L14" t="n">
-        <v>44.46684937728662</v>
+        <v>44.57537080339557</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89835037046332</v>
+        <v>99.89501913748559</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.73926689903736</v>
+        <v>81.21467983075011</v>
       </c>
       <c r="C15" t="n">
-        <v>37.62933060384331</v>
+        <v>37.0202106323205</v>
       </c>
       <c r="D15" t="n">
-        <v>1.390942435755344</v>
+        <v>1.36923515143594</v>
       </c>
       <c r="E15" t="n">
-        <v>12.04272367200901</v>
+        <v>11.83581920432322</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564944398647448</v>
+        <v>0.7565066724501499</v>
       </c>
       <c r="G15" t="n">
-        <v>23.47825468039962</v>
+        <v>23.09862176893429</v>
       </c>
       <c r="H15" t="n">
-        <v>36.79574678459664</v>
+        <v>36.79561064054702</v>
       </c>
       <c r="I15" t="n">
-        <v>2.547014637257331</v>
+        <v>2.630719690246068</v>
       </c>
       <c r="J15" t="n">
-        <v>4.728090249154656</v>
+        <v>4.728166702813438</v>
       </c>
       <c r="K15" t="n">
-        <v>18.26073310096265</v>
+        <v>18.78532016924989</v>
       </c>
       <c r="L15" t="n">
-        <v>44.02512389975347</v>
+        <v>44.10687312298607</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91518760455943</v>
+        <v>99.91240392455646</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.97392905310016</v>
+        <v>78.57627214549497</v>
       </c>
       <c r="C16" t="n">
-        <v>35.25682941504392</v>
+        <v>34.78715284664487</v>
       </c>
       <c r="D16" t="n">
-        <v>1.287890702748512</v>
+        <v>1.270906489517616</v>
       </c>
       <c r="E16" t="n">
-        <v>11.50457514496528</v>
+        <v>11.35157328945728</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571727685470868</v>
+        <v>0.7572108748426243</v>
       </c>
       <c r="G16" t="n">
-        <v>21.73880467111359</v>
+        <v>21.43984418911911</v>
       </c>
       <c r="H16" t="n">
-        <v>36.82874056368727</v>
+        <v>36.82986223143082</v>
       </c>
       <c r="I16" t="n">
-        <v>2.124415398619115</v>
+        <v>2.194307103361125</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732329803419293</v>
+        <v>4.732567967766403</v>
       </c>
       <c r="K16" t="n">
-        <v>21.02607094689985</v>
+        <v>21.42372785450502</v>
       </c>
       <c r="L16" t="n">
-        <v>43.64634923146574</v>
+        <v>43.71604375189884</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92924959340951</v>
+        <v>99.92692445304874</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.83737455305398</v>
+        <v>80.46583213438178</v>
       </c>
       <c r="C17" t="n">
-        <v>36.59737392512615</v>
+        <v>36.1355042171008</v>
       </c>
       <c r="D17" t="n">
-        <v>1.28902340040463</v>
+        <v>1.27207685509088</v>
       </c>
       <c r="E17" t="n">
-        <v>12.34747514841778</v>
+        <v>12.20586799198811</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7578387006936422</v>
+        <v>0.7579081830607555</v>
       </c>
       <c r="G17" t="n">
-        <v>22.23522400297928</v>
+        <v>21.93292802554599</v>
       </c>
       <c r="H17" t="n">
-        <v>37.33843146819497</v>
+        <v>37.33711858758058</v>
       </c>
       <c r="I17" t="n">
-        <v>2.13288995302841</v>
+        <v>2.223006346985734</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736491879335264</v>
+        <v>4.736926144129723</v>
       </c>
       <c r="K17" t="n">
-        <v>19.16262544694602</v>
+        <v>19.53416786561823</v>
       </c>
       <c r="L17" t="n">
-        <v>44.16896677031571</v>
+        <v>44.25629588110547</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92896614238788</v>
+        <v>99.92596796382449</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.19568783046665</v>
+        <v>77.95566033425534</v>
       </c>
       <c r="C18" t="n">
-        <v>34.2841092456064</v>
+        <v>33.96736013708513</v>
       </c>
       <c r="D18" t="n">
-        <v>1.195001796032551</v>
+        <v>1.182840048315337</v>
       </c>
       <c r="E18" t="n">
-        <v>11.74330737127004</v>
+        <v>11.65861609044497</v>
       </c>
       <c r="F18" t="n">
-        <v>0.758413331760775</v>
+        <v>0.7585090126228125</v>
       </c>
       <c r="G18" t="n">
-        <v>20.6133826666029</v>
+        <v>20.3943225140907</v>
       </c>
       <c r="H18" t="n">
-        <v>37.36674332756556</v>
+        <v>37.36671748242144</v>
       </c>
       <c r="I18" t="n">
-        <v>1.778756013729983</v>
+        <v>1.853973857467494</v>
       </c>
       <c r="J18" t="n">
-        <v>4.740083323504844</v>
+        <v>4.740681328892578</v>
       </c>
       <c r="K18" t="n">
-        <v>21.80431216953334</v>
+        <v>22.04433966574464</v>
       </c>
       <c r="L18" t="n">
-        <v>43.85233164172057</v>
+        <v>43.92655002086509</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94075305686033</v>
+        <v>99.93824982369486</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.16490182839273</v>
+        <v>76.93136368450649</v>
       </c>
       <c r="C19" t="n">
-        <v>33.51995207057337</v>
+        <v>33.2201747279595</v>
       </c>
       <c r="D19" t="n">
-        <v>1.15876825046821</v>
+        <v>1.146855000861528</v>
       </c>
       <c r="E19" t="n">
-        <v>11.63548356186285</v>
+        <v>11.56278079786438</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7589013037504559</v>
+        <v>0.7590194415936332</v>
       </c>
       <c r="G19" t="n">
-        <v>19.98836608289123</v>
+        <v>19.77387458074326</v>
       </c>
       <c r="H19" t="n">
-        <v>37.39078552635856</v>
+        <v>37.3918629386126</v>
       </c>
       <c r="I19" t="n">
-        <v>1.489463954621069</v>
+        <v>1.553099414870895</v>
       </c>
       <c r="J19" t="n">
-        <v>4.74313314844035</v>
+        <v>4.743871509960208</v>
       </c>
       <c r="K19" t="n">
-        <v>22.83509817160728</v>
+        <v>23.06863631549351</v>
       </c>
       <c r="L19" t="n">
-        <v>43.59533288340808</v>
+        <v>43.65945379057171</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95038312558873</v>
+        <v>99.94826483402471</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.51207226936219</v>
+        <v>74.25490345823474</v>
       </c>
       <c r="C20" t="n">
-        <v>31.0955596336396</v>
+        <v>30.78177784685646</v>
       </c>
       <c r="D20" t="n">
-        <v>1.065590284360095</v>
+        <v>1.052972310709346</v>
       </c>
       <c r="E20" t="n">
-        <v>10.90684508489312</v>
+        <v>10.83207372039751</v>
       </c>
       <c r="F20" t="n">
-        <v>0.759322929736433</v>
+        <v>0.7594606836637345</v>
       </c>
       <c r="G20" t="n">
-        <v>18.38107722536888</v>
+        <v>18.15516555564639</v>
       </c>
       <c r="H20" t="n">
-        <v>37.41155888217715</v>
+        <v>37.41360001424446</v>
       </c>
       <c r="I20" t="n">
-        <v>1.241909551973811</v>
+        <v>1.295001900674953</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745768310852706</v>
+        <v>4.746629272898341</v>
       </c>
       <c r="K20" t="n">
-        <v>25.4879277306378</v>
+        <v>25.74509654176525</v>
       </c>
       <c r="L20" t="n">
-        <v>43.37513863698313</v>
+        <v>43.42998396096522</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95862600126054</v>
+        <v>99.95685834958694</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.99631950637153</v>
+        <v>80.53095145960445</v>
       </c>
       <c r="C21" t="n">
-        <v>35.15466391768036</v>
+        <v>34.65663885579755</v>
       </c>
       <c r="D21" t="n">
-        <v>1.066358695361545</v>
+        <v>1.053792155146136</v>
       </c>
       <c r="E21" t="n">
-        <v>13.08310040313685</v>
+        <v>12.92724591957791</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598704873685048</v>
+        <v>0.7600519998931646</v>
       </c>
       <c r="G21" t="n">
-        <v>20.27068481680109</v>
+        <v>19.94253244663366</v>
       </c>
       <c r="H21" t="n">
-        <v>39.31488960123414</v>
+        <v>39.21596152587995</v>
       </c>
       <c r="I21" t="n">
-        <v>1.752224956416252</v>
+        <v>1.881042413141365</v>
       </c>
       <c r="J21" t="n">
-        <v>4.749190546053155</v>
+        <v>4.750324999332278</v>
       </c>
       <c r="K21" t="n">
-        <v>19.00368049362847</v>
+        <v>19.46904854039554</v>
       </c>
       <c r="L21" t="n">
-        <v>45.78329017819993</v>
+        <v>45.81165997138676</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94163458950875</v>
+        <v>99.93734736757986</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_47_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_47_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.64298737301479</v>
+        <v>44.53260160928217</v>
       </c>
       <c r="M2" t="n">
-        <v>98.97061130474532</v>
+        <v>92.90128552654704</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.92962951200913</v>
+        <v>81.56028016130162</v>
       </c>
       <c r="C3" t="n">
-        <v>45.88087393732962</v>
+        <v>43.31583571685717</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228516087881618</v>
+        <v>2.184970826054551</v>
       </c>
       <c r="E3" t="n">
-        <v>5.673709723820384</v>
+        <v>4.153903995263627</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428386959605395</v>
+        <v>0.7376917706487007</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95754619875726</v>
+        <v>32.86560284190387</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17058001418481</v>
+        <v>33.93382144984023</v>
       </c>
       <c r="I3" t="n">
-        <v>6.513696941651128</v>
+        <v>3.073715711036253</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642741849753372</v>
+        <v>4.61057356655438</v>
       </c>
       <c r="K3" t="n">
-        <v>12.07037048799089</v>
+        <v>18.43971983869838</v>
       </c>
       <c r="L3" t="n">
-        <v>48.81492474968982</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7661691750103</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.96605940038383</v>
+        <v>88.67614795330242</v>
       </c>
       <c r="C4" t="n">
-        <v>42.54372072557938</v>
+        <v>42.91748171752824</v>
       </c>
       <c r="D4" t="n">
-        <v>2.181757099414274</v>
+        <v>2.190720071364898</v>
       </c>
       <c r="E4" t="n">
-        <v>6.461229549135017</v>
+        <v>6.542479404458755</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443874208628843</v>
+        <v>0.739632835903353</v>
       </c>
       <c r="G4" t="n">
-        <v>33.24504494300175</v>
+        <v>33.55757683144652</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24182135969268</v>
+        <v>34.02311045155424</v>
       </c>
       <c r="I4" t="n">
-        <v>5.439397647884189</v>
+        <v>6.999923134178702</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652421380393027</v>
+        <v>4.622705224395957</v>
       </c>
       <c r="K4" t="n">
-        <v>13.03394059961619</v>
+        <v>11.32385204669757</v>
       </c>
       <c r="L4" t="n">
-        <v>44.24140264864746</v>
+        <v>45.52594780934259</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81906397384301</v>
+        <v>99.7672815735684</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.66041950748195</v>
+        <v>87.65449669727609</v>
       </c>
       <c r="C5" t="n">
-        <v>42.08225101505153</v>
+        <v>42.98096943356089</v>
       </c>
       <c r="D5" t="n">
-        <v>2.117487239619543</v>
+        <v>2.142549916452224</v>
       </c>
       <c r="E5" t="n">
-        <v>7.027702467558918</v>
+        <v>7.372994549052246</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457027482263286</v>
+        <v>0.7412771970650371</v>
       </c>
       <c r="G5" t="n">
-        <v>32.2657176026989</v>
+        <v>32.81970361085855</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30232641841111</v>
+        <v>34.09875106499171</v>
       </c>
       <c r="I5" t="n">
-        <v>4.540840854552597</v>
+        <v>5.846237877199839</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660642176414553</v>
+        <v>4.632982481656483</v>
       </c>
       <c r="K5" t="n">
-        <v>14.33958049251806</v>
+        <v>12.34550330272391</v>
       </c>
       <c r="L5" t="n">
-        <v>43.42707411332253</v>
+        <v>44.47908495443245</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84890562089211</v>
+        <v>99.80555769071725</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.05584692325668</v>
+        <v>86.43441653437469</v>
       </c>
       <c r="C6" t="n">
-        <v>41.1827098147885</v>
+        <v>42.66842259347106</v>
       </c>
       <c r="D6" t="n">
-        <v>2.038498703790503</v>
+        <v>2.084719557161738</v>
       </c>
       <c r="E6" t="n">
-        <v>7.397168535433005</v>
+        <v>7.987493240680295</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468234338192851</v>
+        <v>0.7426725518634911</v>
       </c>
       <c r="G6" t="n">
-        <v>31.06211092057865</v>
+        <v>31.93385482056946</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35387795568711</v>
+        <v>34.1629373857206</v>
       </c>
       <c r="I6" t="n">
-        <v>3.789720912577577</v>
+        <v>4.881035529232287</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667646461370532</v>
+        <v>4.641703449146821</v>
       </c>
       <c r="K6" t="n">
-        <v>15.94415307674333</v>
+        <v>13.56558346562533</v>
       </c>
       <c r="L6" t="n">
-        <v>42.74700264028616</v>
+        <v>43.60359844431473</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87386553181798</v>
+        <v>99.83760450341111</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.28158414216244</v>
+        <v>84.90010928824826</v>
       </c>
       <c r="C7" t="n">
-        <v>39.99668893927412</v>
+        <v>41.89235452543082</v>
       </c>
       <c r="D7" t="n">
-        <v>1.951686263952242</v>
+        <v>2.011786202448885</v>
       </c>
       <c r="E7" t="n">
-        <v>7.609173721944708</v>
+        <v>8.38705889598903</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477801343315265</v>
+        <v>0.7438604869478387</v>
       </c>
       <c r="G7" t="n">
-        <v>29.73928563227802</v>
+        <v>30.81665747238117</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39788617925021</v>
+        <v>34.21758239960059</v>
       </c>
       <c r="I7" t="n">
-        <v>3.162146370833698</v>
+        <v>4.07403578745675</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673625839572041</v>
+        <v>4.649128043423993</v>
       </c>
       <c r="K7" t="n">
-        <v>17.71841585783754</v>
+        <v>15.09989071175175</v>
       </c>
       <c r="L7" t="n">
-        <v>42.17962517753895</v>
+        <v>42.87217044256099</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89472997465062</v>
+        <v>99.86441567974356</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.16139698251179</v>
+        <v>83.22181960535937</v>
       </c>
       <c r="C8" t="n">
-        <v>42.21739990697387</v>
+        <v>40.84691167869147</v>
       </c>
       <c r="D8" t="n">
-        <v>1.955937262579417</v>
+        <v>1.932494407717984</v>
       </c>
       <c r="E8" t="n">
-        <v>9.391626418761371</v>
+        <v>8.623103265791611</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494088860336747</v>
+        <v>0.7448733893264959</v>
       </c>
       <c r="G8" t="n">
-        <v>30.21238172405257</v>
+        <v>29.60206117202972</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47280875754903</v>
+        <v>34.26417590901882</v>
       </c>
       <c r="I8" t="n">
-        <v>5.695428395825255</v>
+        <v>3.399652778184137</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683805537710468</v>
+        <v>4.655458683290601</v>
       </c>
       <c r="K8" t="n">
-        <v>12.83860301748823</v>
+        <v>16.77818039464064</v>
       </c>
       <c r="L8" t="n">
-        <v>44.75456207370834</v>
+        <v>42.2617402659052</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81056499817043</v>
+        <v>99.88683233923732</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84.93822839817666</v>
+        <v>81.32510790362147</v>
       </c>
       <c r="C9" t="n">
-        <v>40.87721742873434</v>
+        <v>39.47799453009795</v>
       </c>
       <c r="D9" t="n">
-        <v>1.854762886565128</v>
+        <v>1.84336005763954</v>
       </c>
       <c r="E9" t="n">
-        <v>9.698335485803254</v>
+        <v>8.698094272169984</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750807343328146</v>
+        <v>0.7457393426222997</v>
       </c>
       <c r="G9" t="n">
-        <v>28.64959189059676</v>
+        <v>28.23669603927004</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53713779309471</v>
+        <v>34.3040097606258</v>
       </c>
       <c r="I9" t="n">
-        <v>4.755047102987752</v>
+        <v>2.836337539904438</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692545895800913</v>
+        <v>4.660870891389375</v>
       </c>
       <c r="K9" t="n">
-        <v>15.06177160182332</v>
+        <v>18.67489209637852</v>
       </c>
       <c r="L9" t="n">
-        <v>43.90280462511388</v>
+        <v>41.75267857412954</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84179365567155</v>
+        <v>99.90556520060602</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.50332043066362</v>
+        <v>86.03624897332411</v>
       </c>
       <c r="C10" t="n">
-        <v>39.17901284752852</v>
+        <v>42.66755104387646</v>
       </c>
       <c r="D10" t="n">
-        <v>1.745221727386077</v>
+        <v>1.845491516335875</v>
       </c>
       <c r="E10" t="n">
-        <v>9.787039953061496</v>
+        <v>10.53050707277576</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520112844614399</v>
+        <v>0.7466016335244181</v>
       </c>
       <c r="G10" t="n">
-        <v>26.95756455468505</v>
+        <v>29.59428688141318</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59251908522624</v>
+        <v>35.66861617660715</v>
       </c>
       <c r="I10" t="n">
-        <v>3.968893297959323</v>
+        <v>2.984485483140107</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700070527884001</v>
+        <v>4.666260209527615</v>
       </c>
       <c r="K10" t="n">
-        <v>17.49667956933639</v>
+        <v>13.96375102667591</v>
       </c>
       <c r="L10" t="n">
-        <v>43.19222294138542</v>
+        <v>43.26932997817235</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86791535825033</v>
+        <v>99.90063204872473</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79.89652632177739</v>
+        <v>85.65394659981335</v>
       </c>
       <c r="C11" t="n">
-        <v>37.18627859097997</v>
+        <v>42.64915141441215</v>
       </c>
       <c r="D11" t="n">
-        <v>1.62927157086785</v>
+        <v>1.820733297979028</v>
       </c>
       <c r="E11" t="n">
-        <v>9.688799203315517</v>
+        <v>10.86842783512028</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530503981528359</v>
+        <v>0.7473369549604696</v>
       </c>
       <c r="G11" t="n">
-        <v>25.16654065186696</v>
+        <v>29.25465810354042</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64031831503045</v>
+        <v>35.76113969499736</v>
       </c>
       <c r="I11" t="n">
-        <v>3.311981194088543</v>
+        <v>2.530794744712846</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706564988455225</v>
+        <v>4.670855968502937</v>
       </c>
       <c r="K11" t="n">
-        <v>20.10347367822261</v>
+        <v>14.34605340018666</v>
       </c>
       <c r="L11" t="n">
-        <v>42.60000069474301</v>
+        <v>42.92051836408358</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8897529639456</v>
+        <v>99.91572317868238</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.2615552284622</v>
+        <v>83.69732342524944</v>
       </c>
       <c r="C12" t="n">
-        <v>35.06268811895584</v>
+        <v>41.08603228713531</v>
       </c>
       <c r="D12" t="n">
-        <v>1.513405328411468</v>
+        <v>1.73725769426178</v>
       </c>
       <c r="E12" t="n">
-        <v>9.460322496134882</v>
+        <v>10.72193512549273</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539481646693419</v>
+        <v>0.7479651930179029</v>
       </c>
       <c r="G12" t="n">
-        <v>23.37681292746777</v>
+        <v>27.91341265620041</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68161557478972</v>
+        <v>35.79120178249948</v>
       </c>
       <c r="I12" t="n">
-        <v>2.763274707805633</v>
+        <v>2.110768517415242</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712176029183388</v>
+        <v>4.674782456361895</v>
       </c>
       <c r="K12" t="n">
-        <v>22.73844477153779</v>
+        <v>16.30267657475056</v>
       </c>
       <c r="L12" t="n">
-        <v>42.1068676318928</v>
+        <v>42.54099128409433</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90800052238643</v>
+        <v>99.92970014598021</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.64022778070726</v>
+        <v>84.86019376345274</v>
       </c>
       <c r="C13" t="n">
-        <v>32.8669496227904</v>
+        <v>42.05687370244879</v>
       </c>
       <c r="D13" t="n">
-        <v>1.399354759400129</v>
+        <v>1.738601397213081</v>
       </c>
       <c r="E13" t="n">
-        <v>9.131573681491728</v>
+        <v>11.36283210506993</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547242990784411</v>
+        <v>0.7485437157325515</v>
       </c>
       <c r="G13" t="n">
-        <v>21.61513099996471</v>
+        <v>28.23942588148419</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71731775760828</v>
+        <v>36.12330817895396</v>
       </c>
       <c r="I13" t="n">
-        <v>2.305099413923712</v>
+        <v>1.969084261670605</v>
       </c>
       <c r="J13" t="n">
-        <v>4.717026869240257</v>
+        <v>4.678398223328449</v>
       </c>
       <c r="K13" t="n">
-        <v>25.35977221929273</v>
+        <v>15.13980623654725</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69652052714447</v>
+        <v>42.73773464677923</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92324236922761</v>
+        <v>99.93441458577527</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.08924032064726</v>
+        <v>82.8879313479602</v>
       </c>
       <c r="C14" t="n">
-        <v>37.40888865473728</v>
+        <v>40.39062460923924</v>
       </c>
       <c r="D14" t="n">
-        <v>1.401146633481525</v>
+        <v>1.656750620560887</v>
       </c>
       <c r="E14" t="n">
-        <v>11.66299366203275</v>
+        <v>11.10155132595958</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556907237116757</v>
+        <v>0.7490379972239516</v>
       </c>
       <c r="G14" t="n">
-        <v>23.63695972577397</v>
+        <v>26.90995557028078</v>
       </c>
       <c r="H14" t="n">
-        <v>36.75592383648182</v>
+        <v>36.14716127165346</v>
       </c>
       <c r="I14" t="n">
-        <v>3.153458715967542</v>
+        <v>1.641987079631843</v>
       </c>
       <c r="J14" t="n">
-        <v>4.723067023197974</v>
+        <v>4.681487482649699</v>
       </c>
       <c r="K14" t="n">
-        <v>17.91075967935275</v>
+        <v>17.1120686520398</v>
       </c>
       <c r="L14" t="n">
-        <v>44.57537080339557</v>
+        <v>42.44260995367458</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89501913748559</v>
+        <v>99.94530321495361</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.21467983075011</v>
+        <v>82.02176480093435</v>
       </c>
       <c r="C15" t="n">
-        <v>37.0202106323205</v>
+        <v>39.76064324078773</v>
       </c>
       <c r="D15" t="n">
-        <v>1.36923515143594</v>
+        <v>1.620588849925423</v>
       </c>
       <c r="E15" t="n">
-        <v>11.83581920432322</v>
+        <v>11.09041284196916</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7565066724501499</v>
+        <v>0.7494602224437109</v>
       </c>
       <c r="G15" t="n">
-        <v>23.09862176893429</v>
+        <v>26.32259400296562</v>
       </c>
       <c r="H15" t="n">
-        <v>36.79561064054702</v>
+        <v>36.16753706456138</v>
       </c>
       <c r="I15" t="n">
-        <v>2.630719690246068</v>
+        <v>1.387045428795864</v>
       </c>
       <c r="J15" t="n">
-        <v>4.728166702813438</v>
+        <v>4.684126390273195</v>
       </c>
       <c r="K15" t="n">
-        <v>18.78532016924989</v>
+        <v>17.97823519906563</v>
       </c>
       <c r="L15" t="n">
-        <v>44.10687312298607</v>
+        <v>42.21491275995814</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91240392455646</v>
+        <v>99.95379119981149</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.57627214549497</v>
+        <v>79.68950531977157</v>
       </c>
       <c r="C16" t="n">
-        <v>34.78715284664487</v>
+        <v>37.64344163458498</v>
       </c>
       <c r="D16" t="n">
-        <v>1.270906489517616</v>
+        <v>1.524495655014534</v>
       </c>
       <c r="E16" t="n">
-        <v>11.35157328945728</v>
+        <v>10.62554260389599</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7572108748426243</v>
+        <v>0.7498227538777785</v>
       </c>
       <c r="G16" t="n">
-        <v>21.43984418911911</v>
+        <v>24.76178963472405</v>
       </c>
       <c r="H16" t="n">
-        <v>36.82986223143082</v>
+        <v>36.18503214793746</v>
       </c>
       <c r="I16" t="n">
-        <v>2.194307103361125</v>
+        <v>1.156430312585638</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732567967766403</v>
+        <v>4.686392211736118</v>
       </c>
       <c r="K16" t="n">
-        <v>21.42372785450502</v>
+        <v>20.31049468022844</v>
       </c>
       <c r="L16" t="n">
-        <v>43.71604375189884</v>
+        <v>42.00753464549779</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92692445304874</v>
+        <v>99.9614709603112</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.46583213438178</v>
+        <v>84.53524509082409</v>
       </c>
       <c r="C17" t="n">
-        <v>36.1355042171008</v>
+        <v>40.80966641869637</v>
       </c>
       <c r="D17" t="n">
-        <v>1.27207685509088</v>
+        <v>1.525306119492581</v>
       </c>
       <c r="E17" t="n">
-        <v>12.20586799198811</v>
+        <v>12.31838935593324</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7579081830607555</v>
+        <v>0.7502213806005574</v>
       </c>
       <c r="G17" t="n">
-        <v>21.93292802554599</v>
+        <v>26.23744512138444</v>
       </c>
       <c r="H17" t="n">
-        <v>37.33711858758058</v>
+        <v>37.66676054943407</v>
       </c>
       <c r="I17" t="n">
-        <v>2.223006346985734</v>
+        <v>1.348238935225722</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736926144129723</v>
+        <v>4.688883628753486</v>
       </c>
       <c r="K17" t="n">
-        <v>19.53416786561823</v>
+        <v>15.46475490917591</v>
       </c>
       <c r="L17" t="n">
-        <v>44.25629588110547</v>
+        <v>43.68066125364135</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92596796382449</v>
+        <v>99.95508258151362</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>77.95566033425534</v>
+        <v>86.23067428867313</v>
       </c>
       <c r="C18" t="n">
-        <v>33.96736013708513</v>
+        <v>41.56662731734545</v>
       </c>
       <c r="D18" t="n">
-        <v>1.182840048315337</v>
+        <v>1.526624437928215</v>
       </c>
       <c r="E18" t="n">
-        <v>11.65861609044497</v>
+        <v>12.94385160545621</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7585090126228125</v>
+        <v>0.7508697951477841</v>
       </c>
       <c r="G18" t="n">
-        <v>20.3943225140907</v>
+        <v>26.38120741551494</v>
       </c>
       <c r="H18" t="n">
-        <v>37.36671748242144</v>
+        <v>37.69931584060372</v>
       </c>
       <c r="I18" t="n">
-        <v>1.853973857467494</v>
+        <v>2.235868974348611</v>
       </c>
       <c r="J18" t="n">
-        <v>4.740681328892578</v>
+        <v>4.692936219673652</v>
       </c>
       <c r="K18" t="n">
-        <v>22.04433966574464</v>
+        <v>13.76932571132687</v>
       </c>
       <c r="L18" t="n">
-        <v>43.92655002086509</v>
+        <v>44.58958236509734</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93824982369486</v>
+        <v>99.92553539376966</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>76.93136368450649</v>
+        <v>83.69518321525419</v>
       </c>
       <c r="C19" t="n">
-        <v>33.2201747279595</v>
+        <v>39.37759953817663</v>
       </c>
       <c r="D19" t="n">
-        <v>1.146855000861528</v>
+        <v>1.432936656688168</v>
       </c>
       <c r="E19" t="n">
-        <v>11.56278079786438</v>
+        <v>12.46026524048283</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7590194415936332</v>
+        <v>0.751427404968957</v>
       </c>
       <c r="G19" t="n">
-        <v>19.77387458074326</v>
+        <v>24.76221277099891</v>
       </c>
       <c r="H19" t="n">
-        <v>37.3918629386126</v>
+        <v>37.72731205099874</v>
       </c>
       <c r="I19" t="n">
-        <v>1.553099414870895</v>
+        <v>1.864607810060586</v>
       </c>
       <c r="J19" t="n">
-        <v>4.743871509960208</v>
+        <v>4.696421281055983</v>
       </c>
       <c r="K19" t="n">
-        <v>23.06863631549351</v>
+        <v>16.30481678474581</v>
       </c>
       <c r="L19" t="n">
-        <v>43.65945379057171</v>
+        <v>44.25547620556789</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94826483402471</v>
+        <v>99.93789252849032</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.25490345823474</v>
+        <v>81.00239652466082</v>
       </c>
       <c r="C20" t="n">
-        <v>30.78177784685646</v>
+        <v>36.97302868949836</v>
       </c>
       <c r="D20" t="n">
-        <v>1.052972310709346</v>
+        <v>1.33396938549517</v>
       </c>
       <c r="E20" t="n">
-        <v>10.83207372039751</v>
+        <v>11.85882297550598</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7594606836637345</v>
+        <v>0.7519081911163623</v>
       </c>
       <c r="G20" t="n">
-        <v>18.15516555564639</v>
+        <v>23.05198460759205</v>
       </c>
       <c r="H20" t="n">
-        <v>37.41360001424446</v>
+        <v>37.75145113468535</v>
       </c>
       <c r="I20" t="n">
-        <v>1.295001900674953</v>
+        <v>1.554834035788657</v>
       </c>
       <c r="J20" t="n">
-        <v>4.746629272898341</v>
+        <v>4.699426194477266</v>
       </c>
       <c r="K20" t="n">
-        <v>25.74509654176525</v>
+        <v>18.99760347533918</v>
       </c>
       <c r="L20" t="n">
-        <v>43.42998396096522</v>
+        <v>43.97757317377188</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95685834958694</v>
+        <v>99.94820533860941</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.53095145960445</v>
+        <v>78.39593490970186</v>
       </c>
       <c r="C21" t="n">
-        <v>34.65663885579755</v>
+        <v>34.60617271638793</v>
       </c>
       <c r="D21" t="n">
-        <v>1.053792155146136</v>
+        <v>1.238722413560605</v>
       </c>
       <c r="E21" t="n">
-        <v>12.92724591957791</v>
+        <v>11.22815737409976</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7600519998931646</v>
+        <v>0.7523226601968334</v>
       </c>
       <c r="G21" t="n">
-        <v>19.94253244663366</v>
+        <v>21.40604598648919</v>
       </c>
       <c r="H21" t="n">
-        <v>39.21596152587995</v>
+        <v>37.77226060241439</v>
       </c>
       <c r="I21" t="n">
-        <v>1.881042413141365</v>
+        <v>1.296409246710898</v>
       </c>
       <c r="J21" t="n">
-        <v>4.750324999332278</v>
+        <v>4.70201662623021</v>
       </c>
       <c r="K21" t="n">
-        <v>19.46904854039554</v>
+        <v>21.60406509029812</v>
       </c>
       <c r="L21" t="n">
-        <v>45.81165997138676</v>
+        <v>43.7465723589865</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93734736757986</v>
+        <v>99.95681016567255</v>
       </c>
     </row>
   </sheetData>
